--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_37.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_37.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TrialPhase</t>
+          <t>Interesting</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Perfectionism</t>
+          <t>Interesting</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.5633730255817044</v>
+        <v>1.167662272109193</v>
       </c>
       <c r="C2">
-        <v>-1.32861573819347</v>
+        <v>0.7026440812980874</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.1383157010603403</v>
+        <v>-2.312384382915952</v>
       </c>
       <c r="C3">
-        <v>-1.872882364732793</v>
+        <v>-0.2147192785546729</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.08648468919832533</v>
+        <v>-1.059403073196503</v>
       </c>
       <c r="C4">
-        <v>0.7340488015078864</v>
+        <v>-1.094428434437933</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.628015287277483</v>
+        <v>0.5886284685434034</v>
       </c>
       <c r="C5">
-        <v>0.1080654382324707</v>
+        <v>-0.1605671318605503</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1419544676350321</v>
+        <v>2.205092511358423</v>
       </c>
       <c r="C6">
-        <v>0.2003031178226247</v>
+        <v>1.00116888051534</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.49483928958211</v>
+        <v>0.3928000201924287</v>
       </c>
       <c r="C7">
-        <v>-1.302589505906685</v>
+        <v>1.507261763515337</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.3894360779873446</v>
+        <v>-0.5577086694555459</v>
       </c>
       <c r="C8">
-        <v>0.2645465771486449</v>
+        <v>-2.097510160829594</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.9496203149661295</v>
+        <v>-0.09945245232544625</v>
       </c>
       <c r="C9">
-        <v>-1.035526604703151</v>
+        <v>0.9565803668296902</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-2.222907481729361</v>
+        <v>-0.3369144256395671</v>
       </c>
       <c r="C10">
-        <v>0.4644592346042745</v>
+        <v>-0.3280271970605675</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.06367905702233</v>
+        <v>-0.6530801283554514</v>
       </c>
       <c r="C11">
-        <v>1.258114627557777</v>
+        <v>-2.080879724416615</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.017986136389076</v>
+        <v>-0.9564028516699903</v>
       </c>
       <c r="C12">
-        <v>0.7720837946534344</v>
+        <v>-1.092984712359972</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.06895747125498566</v>
+        <v>0.8590844433572135</v>
       </c>
       <c r="C13">
-        <v>-0.06289146629362913</v>
+        <v>-0.363343925428318</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.4304771879016687</v>
+        <v>2.467296188451474</v>
       </c>
       <c r="C14">
-        <v>-1.00251948726354</v>
+        <v>0.5951751326745472</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.01796944608555008</v>
+        <v>0.6706477952479696</v>
       </c>
       <c r="C15">
-        <v>-0.6257515163187428</v>
+        <v>-0.3501701327193644</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.4790096862750111</v>
+        <v>0.213029974729198</v>
       </c>
       <c r="C16">
-        <v>1.19489200413502</v>
+        <v>0.3231676692697594</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>3.144239579978452</v>
+        <v>-0.4662274210900779</v>
       </c>
       <c r="C17">
-        <v>2.03056553721701</v>
+        <v>-1.442723240358913</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.3274824906877004</v>
+        <v>-0.4100548058338661</v>
       </c>
       <c r="C18">
-        <v>2.377915610300668</v>
+        <v>-0.01477354617783458</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.073461296280205</v>
+        <v>-0.6675750515133427</v>
       </c>
       <c r="C19">
-        <v>0.9953110778320211</v>
+        <v>-0.7501642907591124</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-0.9255372191805092</v>
+        <v>-1.297647891731741</v>
       </c>
       <c r="C20">
-        <v>-0.1397363746053886</v>
+        <v>-1.464370738412381</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-0.08123185488856693</v>
+        <v>0.0771864481194937</v>
       </c>
       <c r="C21">
-        <v>-0.2573070451232367</v>
+        <v>-0.5907936790509546</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.3180052035069092</v>
+        <v>0.5753012619181385</v>
       </c>
       <c r="C22">
-        <v>0.4047772948365692</v>
+        <v>-0.1538426736200155</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.682814530414169</v>
+        <v>0.1017790745559216</v>
       </c>
       <c r="C23">
-        <v>-1.173604423295761</v>
+        <v>0.1430033231608115</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.127290587228169</v>
+        <v>0.6912206594195014</v>
       </c>
       <c r="C24">
-        <v>1.624867144751556</v>
+        <v>0.558569932688559</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.3439559294873349</v>
+        <v>-1.356942762625786</v>
       </c>
       <c r="C25">
-        <v>-0.4301807760708024</v>
+        <v>-1.715906862259742</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.4256512381635659</v>
+        <v>0.3433854762051915</v>
       </c>
       <c r="C26">
-        <v>-0.004439058409433145</v>
+        <v>-0.322370815963858</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.627145696306313</v>
+        <v>0.6616490503932838</v>
       </c>
       <c r="C27">
-        <v>-0.1063070266828174</v>
+        <v>-1.097348757625181</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>1.560234415090607</v>
+        <v>-0.06781312565777919</v>
       </c>
       <c r="C28">
-        <v>1.575253280309604</v>
+        <v>0.205188127889058</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.171157094426174</v>
+        <v>-1.529369328271166</v>
       </c>
       <c r="C29">
-        <v>0.07359859935080344</v>
+        <v>-0.2507155307950981</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.392228099317533</v>
+        <v>0.4793188473145304</v>
       </c>
       <c r="C30">
-        <v>-1.443455890995349</v>
+        <v>0.7715915698294087</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.7576963247358814</v>
+        <v>0.004398971244163714</v>
       </c>
       <c r="C31">
-        <v>2.067963321800606</v>
+        <v>0.4686372327134784</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.5178832799615009</v>
+        <v>-1.043572621370721</v>
       </c>
       <c r="C32">
-        <v>0.6295125205877765</v>
+        <v>-0.7420236892497609</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.4778124885039399</v>
+        <v>0.9965824928555598</v>
       </c>
       <c r="C33">
-        <v>0.5193828636906367</v>
+        <v>2.035391974046811</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.4236178219343</v>
+        <v>0.6792030421746689</v>
       </c>
       <c r="C34">
-        <v>-0.7431135017909682</v>
+        <v>-0.5987790847035683</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.6839967563827363</v>
+        <v>-0.4983423947053001</v>
       </c>
       <c r="C35">
-        <v>-0.1506592893498311</v>
+        <v>0.8389030423907524</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.4884599386268574</v>
+        <v>0.7320309341607014</v>
       </c>
       <c r="C36">
-        <v>-0.5770776215261888</v>
+        <v>-1.124225134546465</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.925946967136247</v>
+        <v>2.318046706510366</v>
       </c>
       <c r="C37">
-        <v>0.8678194476791772</v>
+        <v>1.469551012455878</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.438386702316366</v>
+        <v>0.08644569082775228</v>
       </c>
       <c r="C38">
-        <v>0.618506401869697</v>
+        <v>0.135601244090838</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.4077656792231628</v>
+        <v>-0.5211917174368516</v>
       </c>
       <c r="C39">
-        <v>0.5822350251030425</v>
+        <v>0.2465780212054037</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.7334043144482096</v>
+        <v>1.215600252882982</v>
       </c>
       <c r="C40">
-        <v>1.576835221580074</v>
+        <v>0.7280977166886355</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.130546044849444</v>
+        <v>-0.2092275701671103</v>
       </c>
       <c r="C41">
-        <v>-0.2016274289387359</v>
+        <v>0.3294614532491834</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.722479697338082</v>
+        <v>-0.5844063019953446</v>
       </c>
       <c r="C42">
-        <v>-0.9282304699517944</v>
+        <v>-0.4742160146371541</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.335005806320403</v>
+        <v>1.455727641620734</v>
       </c>
       <c r="C43">
-        <v>2.010614264929888</v>
+        <v>1.76290704682326</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.6770050917123014</v>
+        <v>-0.7074408599164286</v>
       </c>
       <c r="C44">
-        <v>0.1172946444164022</v>
+        <v>-0.2307181693036899</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.828098119292597</v>
+        <v>-1.850492105489729</v>
       </c>
       <c r="C45">
-        <v>1.599702482563946</v>
+        <v>-0.4843597027577086</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.499389932636672</v>
+        <v>0.229787097609134</v>
       </c>
       <c r="C46">
-        <v>-1.101788954633468</v>
+        <v>1.242743826250869</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.43454012997854</v>
+        <v>-0.6767272573800382</v>
       </c>
       <c r="C47">
-        <v>-0.01863058749539351</v>
+        <v>0.03925964284171074</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.8060529697771897</v>
+        <v>1.327228015585511</v>
       </c>
       <c r="C48">
-        <v>0.8451430547169114</v>
+        <v>1.181220916706855</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.7021440724843201</v>
+        <v>0.6639220032065125</v>
       </c>
       <c r="C49">
-        <v>-1.652060471494232</v>
+        <v>0.2406435985081705</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.7356793478541256</v>
+        <v>1.37975158016001</v>
       </c>
       <c r="C50">
-        <v>0.7443967223936343</v>
+        <v>0.9467193720984537</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.191247885719055</v>
+        <v>-1.252910822636242</v>
       </c>
       <c r="C51">
-        <v>-0.8115460406940411</v>
+        <v>-0.8898429266180239</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.8158529510634022</v>
+        <v>-1.525436239169443</v>
       </c>
       <c r="C52">
-        <v>0.2852754897689583</v>
+        <v>-0.5483427275531507</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>0.7741318710152925</v>
+        <v>0.4664477787175262</v>
       </c>
       <c r="C53">
-        <v>0.165509218294902</v>
+        <v>-0.4913049630935691</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.6756466093812779</v>
+        <v>-0.8857985185373087</v>
       </c>
       <c r="C54">
-        <v>-2.400434135173805</v>
+        <v>0.3654850080707213</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.8497833934817084</v>
+        <v>0.2313201552396906</v>
       </c>
       <c r="C55">
-        <v>0.6224197057356</v>
+        <v>0.5169789293679685</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-1.366150482304277</v>
+        <v>-0.92821130990393</v>
       </c>
       <c r="C56">
-        <v>-0.2414685647730339</v>
+        <v>-0.8347262354539802</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-2.166073898856741</v>
+        <v>-1.666815573574188</v>
       </c>
       <c r="C57">
-        <v>-0.6635387768135255</v>
+        <v>-2.162056320339787</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>1.641694885243933</v>
+        <v>-0.9656830395606996</v>
       </c>
       <c r="C58">
-        <v>0.305752230202965</v>
+        <v>-2.35599316337111</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>2.649178296073914</v>
+        <v>0.1129932687815364</v>
       </c>
       <c r="C59">
-        <v>-0.6302100119767924</v>
+        <v>-1.565453045383099</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.2108073613202801</v>
+        <v>-1.819012650394168</v>
       </c>
       <c r="C60">
-        <v>0.03447390592783152</v>
+        <v>-0.05460770895904077</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.1922831850371577</v>
+        <v>-1.140578233622518</v>
       </c>
       <c r="C61">
-        <v>-0.2740163136406225</v>
+        <v>-0.3957365493418495</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.5343569035217318</v>
+        <v>0.3456526705645553</v>
       </c>
       <c r="C62">
-        <v>1.009774614492605</v>
+        <v>0.5032349291173426</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.8101171199254947</v>
+        <v>-1.325751997658018</v>
       </c>
       <c r="C63">
-        <v>0.665283528898109</v>
+        <v>-0.6786510503955523</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.4282232165102376</v>
+        <v>0.04544487199477251</v>
       </c>
       <c r="C64">
-        <v>0.573474345342725</v>
+        <v>-1.101984766365635</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.052566112502291</v>
+        <v>-0.2951006534353566</v>
       </c>
       <c r="C65">
-        <v>-1.718904330296055</v>
+        <v>0.3056594107816716</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>-0.1824982964705514</v>
+        <v>0.2194038466390635</v>
       </c>
       <c r="C66">
-        <v>2.430863757960137</v>
+        <v>-2.099792270268411</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-1.132206282760197</v>
+        <v>1.962267721531057</v>
       </c>
       <c r="C67">
-        <v>1.360915807563867</v>
+        <v>-0.6489475837485962</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-2.732444115290765</v>
+        <v>1.921961967766915</v>
       </c>
       <c r="C68">
-        <v>1.033125972172575</v>
+        <v>-0.05853728091335764</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>-0.1459791917337609</v>
+        <v>-0.9963952193406493</v>
       </c>
       <c r="C69">
-        <v>-0.1999421735178928</v>
+        <v>0.4140738809832848</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>0.06846265422447502</v>
+        <v>-0.6501997706398799</v>
       </c>
       <c r="C70">
-        <v>1.40522147823246</v>
+        <v>0.2090008963666496</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>1.743922068422139</v>
+        <v>-0.6605923051241696</v>
       </c>
       <c r="C71">
-        <v>-2.093583804351991</v>
+        <v>-2.417078724063642</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-0.4007723740986621</v>
+        <v>-1.516885723815302</v>
       </c>
       <c r="C72">
-        <v>1.326744561468008</v>
+        <v>-0.3666554175037092</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>0.6483268048378343</v>
+        <v>-1.060883465253544</v>
       </c>
       <c r="C73">
-        <v>1.104957998521598</v>
+        <v>-0.0303171252155886</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.8223581242997549</v>
+        <v>-2.001388025719352</v>
       </c>
       <c r="C74">
-        <v>-0.9040476081186457</v>
+        <v>0.6954992480929961</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-1.240097521303467</v>
+        <v>1.369275300308886</v>
       </c>
       <c r="C75">
-        <v>0.4299429428160387</v>
+        <v>-0.009724773741362269</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.7079642526533586</v>
+        <v>-0.6810264448713791</v>
       </c>
       <c r="C76">
-        <v>1.325802396565964</v>
+        <v>0.7216805246251341</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-1.604068529681562</v>
+        <v>0.5292026505364318</v>
       </c>
       <c r="C77">
-        <v>-0.3806118814887975</v>
+        <v>0.2889194243809384</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.0570683779123014</v>
+        <v>-0.5377576248885257</v>
       </c>
       <c r="C78">
-        <v>2.125374259975942</v>
+        <v>0.2370080121566001</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.1558904976977048</v>
+        <v>-0.2745969093022693</v>
       </c>
       <c r="C79">
-        <v>0.7828533009415534</v>
+        <v>-1.130423554396221</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.4815464233168069</v>
+        <v>1.460652493120038</v>
       </c>
       <c r="C80">
-        <v>-0.01006341486650372</v>
+        <v>0.8174435322683852</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-1.195780650953586</v>
+        <v>0.9652576622728283</v>
       </c>
       <c r="C81">
-        <v>-0.471093379292528</v>
+        <v>0.6347286000719772</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>-0.1881882076484557</v>
+        <v>0.1508845767056232</v>
       </c>
       <c r="C82">
-        <v>-0.43876774530705</v>
+        <v>0.3301702504237799</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.07521310709587484</v>
+        <v>-0.03031398182061313</v>
       </c>
       <c r="C83">
-        <v>-0.5542125753153326</v>
+        <v>1.061169095976519</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>-0.9365684306585886</v>
+        <v>-0.6817013514715358</v>
       </c>
       <c r="C84">
-        <v>0.07171854327248925</v>
+        <v>0.2108323236021467</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>-1.096077578986741</v>
+        <v>0.8012860358555397</v>
       </c>
       <c r="C85">
-        <v>0.3414651973822543</v>
+        <v>-0.7409799898908866</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-0.1103501420063878</v>
+        <v>1.568539946370024</v>
       </c>
       <c r="C86">
-        <v>0.4666849407296689</v>
+        <v>-0.2987007464768495</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.245285390679717</v>
+        <v>0.5074623303555411</v>
       </c>
       <c r="C87">
-        <v>-0.4466461323149985</v>
+        <v>-0.2352116234040622</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-1.697108780340088</v>
+        <v>1.761784047029598</v>
       </c>
       <c r="C88">
-        <v>0.5297260367827727</v>
+        <v>0.6959653678191439</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.066808308010025</v>
+        <v>-0.1705071216890941</v>
       </c>
       <c r="C89">
-        <v>0.9862957978111262</v>
+        <v>1.076206684777176</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-1.052733416013407</v>
+        <v>-0.9473668676716088</v>
       </c>
       <c r="C90">
-        <v>-0.6618085314647988</v>
+        <v>-2.12236504036862</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>1.519323380114526</v>
+        <v>-1.694096948828432</v>
       </c>
       <c r="C91">
-        <v>0.157993503578905</v>
+        <v>0.9598879755020888</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>1.762921963469763</v>
+        <v>0.3934004598066144</v>
       </c>
       <c r="C92">
-        <v>-1.276183561391059</v>
+        <v>-0.8108332616674263</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-1.139037463614875</v>
+        <v>0.07939827570109172</v>
       </c>
       <c r="C93">
-        <v>-1.101116719244121</v>
+        <v>0.7026106555019224</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.2760332892491241</v>
+        <v>-1.506730448860284</v>
       </c>
       <c r="C94">
-        <v>1.086705987066117</v>
+        <v>-0.2069897559081149</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.8374699599769679</v>
+        <v>-0.5406113302116952</v>
       </c>
       <c r="C95">
-        <v>0.8017020137111416</v>
+        <v>-0.4086291736885563</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-0.4458808393267685</v>
+        <v>2.682097926631954</v>
       </c>
       <c r="C96">
-        <v>-0.3120564345345122</v>
+        <v>1.543082085825803</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.763067166966044</v>
+        <v>2.266859456120667</v>
       </c>
       <c r="C97">
-        <v>-0.7163348683119166</v>
+        <v>1.371997860167795</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.9218329070899627</v>
+        <v>-1.375744587071686</v>
       </c>
       <c r="C98">
-        <v>0.4237211379623481</v>
+        <v>-1.34463810460102</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.4095298615106209</v>
+        <v>0.1243102403619014</v>
       </c>
       <c r="C99">
-        <v>0.3408944415443974</v>
+        <v>0.1405293375643199</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>-0.1361503344420518</v>
+        <v>-0.977784253283567</v>
       </c>
       <c r="C100">
-        <v>-0.4777056974176561</v>
+        <v>-0.6350093378845546</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>-1.160260634602648</v>
+        <v>0.3824078879070983</v>
       </c>
       <c r="C101">
-        <v>-0.2271909967100894</v>
+        <v>0.1814517949105655</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>-0.1376476286441632</v>
+        <v>-0.4694136744442521</v>
       </c>
       <c r="C102">
-        <v>0.4771560463363088</v>
+        <v>-1.505122991555684</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>1.595591078310664</v>
+        <v>0.4619968035159113</v>
       </c>
       <c r="C103">
-        <v>-0.4942318644288641</v>
+        <v>-0.5012624780671369</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>1.045179452828787</v>
+        <v>-0.4340384615334053</v>
       </c>
       <c r="C104">
-        <v>0.7508509965284684</v>
+        <v>-0.3125198628043233</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>-1.027597714872403</v>
+        <v>1.048426600317899</v>
       </c>
       <c r="C105">
-        <v>-0.1354495329777252</v>
+        <v>0.7530461440088432</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.2996760040561637</v>
+        <v>-0.306493463320691</v>
       </c>
       <c r="C106">
-        <v>-1.150569698412984</v>
+        <v>-0.9508918838827793</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-1.423299352075473</v>
+        <v>1.624394532311604</v>
       </c>
       <c r="C107">
-        <v>0.2234732739998113</v>
+        <v>0.1008316411363444</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>-0.6183501216567636</v>
+        <v>0.5807185851698312</v>
       </c>
       <c r="C108">
-        <v>-0.3372740846082393</v>
+        <v>0.339873056176499</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.7911450800234358</v>
+        <v>-0.8576659959389477</v>
       </c>
       <c r="C109">
-        <v>-1.112663097304713</v>
+        <v>0.3520268620932578</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.4977649680604205</v>
+        <v>0.523505623223079</v>
       </c>
       <c r="C110">
-        <v>0.4870986787750392</v>
+        <v>-0.9714725155586001</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.3211932319650933</v>
+        <v>-0.1604774223992909</v>
       </c>
       <c r="C111">
-        <v>0.002234826125659918</v>
+        <v>-0.5115674787855652</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>1.937659779276176</v>
+        <v>-0.3176118582802882</v>
       </c>
       <c r="C112">
-        <v>0.5057311508489508</v>
+        <v>0.9932078901634863</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.6197373255459153</v>
+        <v>-0.4455340478059736</v>
       </c>
       <c r="C113">
-        <v>0.1769703310376029</v>
+        <v>-0.7635383944341254</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.08015421094906121</v>
+        <v>1.780904383053727</v>
       </c>
       <c r="C114">
-        <v>-0.308063663767954</v>
+        <v>0.2713618629135011</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-1.395552834614536</v>
+        <v>-1.813464861163595</v>
       </c>
       <c r="C115">
-        <v>0.4095642062414542</v>
+        <v>-0.8279653748278311</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-0.7471742660596546</v>
+        <v>-0.8166606872902591</v>
       </c>
       <c r="C116">
-        <v>0.7954148001260796</v>
+        <v>0.0622879152019426</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.882196908457418</v>
+        <v>-2.071731308247638</v>
       </c>
       <c r="C117">
-        <v>0.5268572072657185</v>
+        <v>-2.329708586510093</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.5801097271015002</v>
+        <v>-1.008283631952794</v>
       </c>
       <c r="C118">
-        <v>-0.8341891262470313</v>
+        <v>-0.9253594064685084</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.1131400257932158</v>
+        <v>1.863834673441765</v>
       </c>
       <c r="C119">
-        <v>-0.3089017710134559</v>
+        <v>1.553547779347208</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.02886415834292073</v>
+        <v>-1.352050222959399</v>
       </c>
       <c r="C120">
-        <v>0.0420310410524969</v>
+        <v>0.3868458724763453</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>-1.277957529858432</v>
+        <v>-1.597923055821218</v>
       </c>
       <c r="C121">
-        <v>0.06040676013108583</v>
+        <v>-1.815438050725311</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>0.7134428666060479</v>
+        <v>-1.07850526834705</v>
       </c>
       <c r="C122">
-        <v>1.176591196466874</v>
+        <v>-0.870403326535049</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.3956729604163635</v>
+        <v>-0.6387258017751115</v>
       </c>
       <c r="C123">
-        <v>0.6221706008105922</v>
+        <v>0.1610471597964312</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.06726591501208</v>
+        <v>0.4705227547740752</v>
       </c>
       <c r="C124">
-        <v>-0.4739132555995379</v>
+        <v>-0.4761664656510556</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.3980782261701477</v>
+        <v>1.316392368598593</v>
       </c>
       <c r="C125">
-        <v>0.8305119301572234</v>
+        <v>-1.624556715274958</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>-0.4667312222039139</v>
+        <v>-0.9248679486109692</v>
       </c>
       <c r="C126">
-        <v>0.7244705641340174</v>
+        <v>-1.34720622370674</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>0.3255485592166324</v>
+        <v>0.2080220650834455</v>
       </c>
       <c r="C127">
-        <v>-0.6516997958955143</v>
+        <v>0.3817590302827283</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>-0.7659934248661011</v>
+        <v>-0.5323539007810419</v>
       </c>
       <c r="C128">
-        <v>0.5747647382148102</v>
+        <v>1.405272380012881</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-0.3113117050596424</v>
+        <v>-0.4416979237336232</v>
       </c>
       <c r="C129">
-        <v>-1.0863997282524</v>
+        <v>-0.5962628439636913</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>-0.04161805970495761</v>
+        <v>-0.666433424666941</v>
       </c>
       <c r="C130">
-        <v>0.5229896555903575</v>
+        <v>2.082440494990716</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>1.89166499089234</v>
+        <v>0.221854079663719</v>
       </c>
       <c r="C131">
-        <v>2.53377263828842</v>
+        <v>-0.5465271681430987</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.777513832425024</v>
+        <v>-0.4036886329301526</v>
       </c>
       <c r="C132">
-        <v>0.8544775343890704</v>
+        <v>-0.1268806809076323</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>1.551295675427667</v>
+        <v>0.897544250009229</v>
       </c>
       <c r="C133">
-        <v>1.432114335069853</v>
+        <v>1.147895621083646</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>0.9339785913594066</v>
+        <v>0.6298594990192881</v>
       </c>
       <c r="C134">
-        <v>-1.142841059854423</v>
+        <v>0.7588334202115219</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>1.376193721005819</v>
+        <v>-1.174407537531574</v>
       </c>
       <c r="C135">
-        <v>-0.3356109921184127</v>
+        <v>0.8227743881787848</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>1.136187122484703</v>
+        <v>-1.817537910831238</v>
       </c>
       <c r="C136">
-        <v>0.468845939138149</v>
+        <v>0.5985543983545443</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.5379201342243991</v>
+        <v>-0.8346488065740819</v>
       </c>
       <c r="C137">
-        <v>-0.4220244700997149</v>
+        <v>-1.525258966202591</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>-1.716993635950984</v>
+        <v>0.144392201293698</v>
       </c>
       <c r="C138">
-        <v>-1.03949237494921</v>
+        <v>-0.1213478380253494</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>-0.3632161267294536</v>
+        <v>-1.455405606258489</v>
       </c>
       <c r="C139">
-        <v>-0.2993980238246889</v>
+        <v>0.8735561381981344</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>-0.03312135726267231</v>
+        <v>-0.6220098918404208</v>
       </c>
       <c r="C140">
-        <v>-0.2624020800436223</v>
+        <v>-1.647365265561775</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>-2.004001354187048</v>
+        <v>-1.422923518916944</v>
       </c>
       <c r="C141">
-        <v>-1.532900983073422</v>
+        <v>-0.7420645175062583</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.027714602536374</v>
+        <v>-0.5573907686626269</v>
       </c>
       <c r="C142">
-        <v>-0.5565558823468489</v>
+        <v>0.1047554785562134</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>1.761355858525091</v>
+        <v>-0.1705807991084564</v>
       </c>
       <c r="C143">
-        <v>1.071764139021733</v>
+        <v>-0.9873264804357759</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>0.009566096921782634</v>
+        <v>-0.6389717924540693</v>
       </c>
       <c r="C144">
-        <v>-0.5338109095458805</v>
+        <v>0.03889757294744334</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>-0.1327129148086097</v>
+        <v>-0.7604621805406232</v>
       </c>
       <c r="C145">
-        <v>-0.6043466604367735</v>
+        <v>-0.006522266558330214</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-1.127807861263118</v>
+        <v>-0.5509845491156665</v>
       </c>
       <c r="C146">
-        <v>-0.6728692172454998</v>
+        <v>-1.306061121950235</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.584345476260276</v>
+        <v>-0.840787068669712</v>
       </c>
       <c r="C147">
-        <v>-0.3165206929773919</v>
+        <v>1.008836615358051</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>-0.9082667175197768</v>
+        <v>-0.01659890957137479</v>
       </c>
       <c r="C148">
-        <v>-1.107632396805767</v>
+        <v>-1.366277784771569</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>2.064927844961704</v>
+        <v>0.6881427636348296</v>
       </c>
       <c r="C149">
-        <v>-2.469122268992855</v>
+        <v>0.2290742752380706</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>0.0291485820931437</v>
+        <v>0.316741473628639</v>
       </c>
       <c r="C150">
-        <v>-0.2768629374798098</v>
+        <v>0.5728733285383304</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.6582880394678984</v>
+        <v>0.6153602431187802</v>
       </c>
       <c r="C151">
-        <v>0.1916649239666217</v>
+        <v>0.9815328571209604</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>-1.15001967506921</v>
+        <v>-0.3135616005768125</v>
       </c>
       <c r="C152">
-        <v>0.8469303388963968</v>
+        <v>-0.09350660571746605</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-0.07466719618331148</v>
+        <v>-0.1665822059114545</v>
       </c>
       <c r="C153">
-        <v>0.7984233967364024</v>
+        <v>-1.05120151264983</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>-1.070507455750404</v>
+        <v>-0.4514160176307206</v>
       </c>
       <c r="C154">
-        <v>1.182335730410767</v>
+        <v>0.3843842415673331</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>-0.09210293852709017</v>
+        <v>-0.1134530115739101</v>
       </c>
       <c r="C155">
-        <v>-2.757328756824107</v>
+        <v>-0.4805186578656012</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>-0.1378598745864788</v>
+        <v>-1.100694995847604</v>
       </c>
       <c r="C156">
-        <v>-0.3596318296684104</v>
+        <v>-0.4733300037425993</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>-1.147655667184063</v>
+        <v>-0.2287290756507277</v>
       </c>
       <c r="C157">
-        <v>-0.1556206189473593</v>
+        <v>0.2491539250158591</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>1.169134695399495</v>
+        <v>-0.417931016575536</v>
       </c>
       <c r="C158">
-        <v>-1.90011488739737</v>
+        <v>-0.2079635517124793</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>0.06496056227902894</v>
+        <v>-0.5963086590703819</v>
       </c>
       <c r="C159">
-        <v>-0.3635110067494035</v>
+        <v>-0.507083055234544</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>0.2910608042791084</v>
+        <v>-0.2545002954457137</v>
       </c>
       <c r="C160">
-        <v>0.8475529534067987</v>
+        <v>-1.21886917766474</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>-2.035135584837651</v>
+        <v>1.307161728242537</v>
       </c>
       <c r="C161">
-        <v>0.6807495617314366</v>
+        <v>0.05516832846891212</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>0.1120965154616613</v>
+        <v>-1.554691206862092</v>
       </c>
       <c r="C162">
-        <v>-0.2219893060653853</v>
+        <v>-0.7093103769331709</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>-0.8191076740334845</v>
+        <v>0.209761529047991</v>
       </c>
       <c r="C163">
-        <v>-2.008076036041605</v>
+        <v>-0.1217794976845429</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>-1.507067868774173</v>
+        <v>0.1346223093782287</v>
       </c>
       <c r="C164">
-        <v>-0.395773273861392</v>
+        <v>-0.6319255260042125</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.7941338500243359</v>
+        <v>-0.115312720827066</v>
       </c>
       <c r="C165">
-        <v>-1.121088830487869</v>
+        <v>-1.533927722810583</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>0.4336481823754426</v>
+        <v>1.153260626362763</v>
       </c>
       <c r="C166">
-        <v>0.7836687553731876</v>
+        <v>0.2346864070961216</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-1.193471023731155</v>
+        <v>0.05302908632115483</v>
       </c>
       <c r="C167">
-        <v>0.9528306907490518</v>
+        <v>0.7076671040804073</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.3501398351756427</v>
+        <v>0.9595062951024262</v>
       </c>
       <c r="C168">
-        <v>-2.03322411548341</v>
+        <v>-0.1736668423014126</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>0.2682965332608243</v>
+        <v>0.7952915232113644</v>
       </c>
       <c r="C169">
-        <v>-0.5517939963153692</v>
+        <v>-1.520133694064616</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>-0.407888835345439</v>
+        <v>1.202011219710074</v>
       </c>
       <c r="C170">
-        <v>0.7184681362184342</v>
+        <v>1.171005932935719</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>-1.125654726800444</v>
+        <v>0.02021916301271692</v>
       </c>
       <c r="C171">
-        <v>-0.9623937461911902</v>
+        <v>0.4587389457660097</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>1.502153835771233</v>
+        <v>-0.1875683244409099</v>
       </c>
       <c r="C172">
-        <v>0.1905627395636765</v>
+        <v>0.4921046129882444</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>2.194103332401873</v>
+        <v>-0.3082237491565329</v>
       </c>
       <c r="C173">
-        <v>0.3278239220125884</v>
+        <v>0.9214380743469176</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>-1.074533487186892</v>
+        <v>0.3808545967456256</v>
       </c>
       <c r="C174">
-        <v>-0.1639433310729893</v>
+        <v>-1.095706353455737</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>0.991545231443686</v>
+        <v>0.177275075287137</v>
       </c>
       <c r="C175">
-        <v>-0.04687444103514628</v>
+        <v>1.190971151279157</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>1.671181118994843</v>
+        <v>-1.239652252194348</v>
       </c>
       <c r="C176">
-        <v>0.7542390490156491</v>
+        <v>0.4045812686189891</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.9708909452714414</v>
+        <v>-1.799373899834735</v>
       </c>
       <c r="C177">
-        <v>2.241092571817791</v>
+        <v>-0.1282929459426717</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>0.0982129030598284</v>
+        <v>-0.5084660689219381</v>
       </c>
       <c r="C178">
-        <v>-1.498137307483147</v>
+        <v>1.770274461432816</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>1.052948904902731</v>
+        <v>-0.4961499843294178</v>
       </c>
       <c r="C179">
-        <v>-0.7704520362943105</v>
+        <v>-0.1752638159300005</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>-0.139686191548149</v>
+        <v>1.106143301572929</v>
       </c>
       <c r="C180">
-        <v>0.7092496567053109</v>
+        <v>1.258941580050486</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>1.106315209501829</v>
+        <v>1.00524306223464</v>
       </c>
       <c r="C181">
-        <v>0.8569646875997012</v>
+        <v>0.6492908899987</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.9245119827488338</v>
+        <v>0.7281880578708201</v>
       </c>
       <c r="C182">
-        <v>-0.03089510639948117</v>
+        <v>0.5110770872758803</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>-0.2148850567528506</v>
+        <v>0.5771829308199863</v>
       </c>
       <c r="C183">
-        <v>1.176366935043282</v>
+        <v>0.3417937969425228</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>1.368934008336536</v>
+        <v>0.09749055927976479</v>
       </c>
       <c r="C184">
-        <v>-0.3940898426740922</v>
+        <v>1.329811448118698</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.6834483540332295</v>
+        <v>1.415713813655185</v>
       </c>
       <c r="C185">
-        <v>0.3421153517118845</v>
+        <v>2.175897976528422</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>-0.4361427114483983</v>
+        <v>-0.2212141021002188</v>
       </c>
       <c r="C186">
-        <v>-0.6162123387216619</v>
+        <v>-0.09772642923828613</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>1.934194883545571</v>
+        <v>0.6101125047481063</v>
       </c>
       <c r="C187">
-        <v>0.9639189105145551</v>
+        <v>0.3108272789147846</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>0.9559604991842929</v>
+        <v>2.561716098397749</v>
       </c>
       <c r="C188">
-        <v>1.585848976130934</v>
+        <v>1.145324083336015</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>0.6737295175790222</v>
+        <v>-0.6942493663746478</v>
       </c>
       <c r="C189">
-        <v>-0.525948389038257</v>
+        <v>0.4202845968298745</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>-0.5868828445572364</v>
+        <v>-1.8977609502178</v>
       </c>
       <c r="C190">
-        <v>0.5144792044799535</v>
+        <v>-1.579418010284011</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>0.2131617181328836</v>
+        <v>0.08494659423203915</v>
       </c>
       <c r="C191">
-        <v>-0.8571072192045514</v>
+        <v>-1.413093375712378</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>1.085026509671073</v>
+        <v>1.622318158085408</v>
       </c>
       <c r="C192">
-        <v>-1.792799778896339</v>
+        <v>1.151729808304442</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-0.7456209222082885</v>
+        <v>2.007880035721965</v>
       </c>
       <c r="C193">
-        <v>-1.661162869375159</v>
+        <v>0.2703900596321531</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>0.6409537275793292</v>
+        <v>1.12676435459175</v>
       </c>
       <c r="C194">
-        <v>1.018285661579681</v>
+        <v>-0.4550449478954309</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>-0.8216303710918923</v>
+        <v>-0.00482669930875893</v>
       </c>
       <c r="C195">
-        <v>-0.5731891128117894</v>
+        <v>-0.352209088753954</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>1.907905312424408</v>
+        <v>-0.6126347265095959</v>
       </c>
       <c r="C196">
-        <v>-1.473241335099108</v>
+        <v>0.4047473148964821</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>0.4550163627414135</v>
+        <v>0.4130218381047724</v>
       </c>
       <c r="C197">
-        <v>1.184127977757966</v>
+        <v>0.5622218353799004</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>-0.2727588989267688</v>
+        <v>1.27622001810094</v>
       </c>
       <c r="C198">
-        <v>0.07851188908966754</v>
+        <v>0.3718343800936827</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>0.603151352225929</v>
+        <v>2.449380798406918</v>
       </c>
       <c r="C199">
-        <v>0.7526192598822158</v>
+        <v>1.04264704268623</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>0.5275638727288275</v>
+        <v>-1.854070993063295</v>
       </c>
       <c r="C200">
-        <v>0.7807757326216147</v>
+        <v>-0.9803298450595846</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>-2.056153294186103</v>
+        <v>-2.375044712430523</v>
       </c>
       <c r="C201">
-        <v>-0.04338739000970358</v>
+        <v>-0.6580472524974629</v>
       </c>
     </row>
   </sheetData>
